--- a/diseases/d157/2015-2019.xlsx
+++ b/diseases/d157/2015-2019.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>27</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.5202541692109344</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>25</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.4817168233434578</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>17</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.3275674398735512</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>21</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.4046421316085045</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>24</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.4624481504097195</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>13</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.250492748138598</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>22</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.4239108045422428</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>13</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.250492748138598</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>7</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.1348807105361682</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>7</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.1348807105361682</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>8</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.1541493834699065</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>22</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.4239108045422428</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>23</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.4392680419321453</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>67</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.6751799808127957</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>25</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.4774652629697232</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>68</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.6852572939592554</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>17</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.3246763788194117</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>65</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.6550253545198765</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>18</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.3437749893382007</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>68</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.6852572939592554</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>27</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.515662484007301</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>59</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.5945614756411186</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>13</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.2482819367442561</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>58</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.5844841624946591</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>17</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.3246763788194117</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>45</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.4534790915906837</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>10</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.1909861051878893</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>34</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.3426286469796277</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>8</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.1527888841503114</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>34</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.3426286469796277</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>11</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.2100847157066782</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>36</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.3627832732725469</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>8</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.1527888841503114</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>37</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.3728605864190066</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>20</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.3819722103757786</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>55</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.5542522230552801</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>30</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.568526110272272</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>71</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.7059154672193487</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>25</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.4737717585602266</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>61</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.6064907535264827</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>33</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.6253787212994991</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>75</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.7456853526964952</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>22</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.4169191475329994</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>69</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.6860305244807755</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>17</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.3221647958209541</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>81</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.8053401809122147</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>12</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.2274104441089087</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>55</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.5468359253107631</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>20</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.3790174068481813</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>42</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.4175837975100373</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>16</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.303213925478545</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>48</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.4772386257257569</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>12</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.2274104441089087</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>32</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.3181590838171713</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>14</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.2653121847937269</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>24</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.2386193128628785</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>23</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.4358700178754085</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>42</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.4175837975100373</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>29</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.5495752399298628</v>
       </c>
@@ -24129,9 +23952,6 @@
       <c r="O120" t="n">
         <v>67</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.6661455817422024</v>
       </c>
@@ -24525,9 +24345,6 @@
       <c r="O122" t="n">
         <v>31</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.583611529339893</v>
       </c>
@@ -24921,9 +24738,6 @@
       <c r="O124" t="n">
         <v>85</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.8353476267208837</v>
       </c>
@@ -25317,9 +25131,6 @@
       <c r="O126" t="n">
         <v>30</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.56478535097409</v>
       </c>
@@ -25713,9 +25524,6 @@
       <c r="O128" t="n">
         <v>102</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>1.00241715206506</v>
       </c>
@@ -26109,9 +25917,6 @@
       <c r="O130" t="n">
         <v>40</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.75304713463212</v>
       </c>
@@ -26505,9 +26310,6 @@
       <c r="O132" t="n">
         <v>127</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>1.248107630512379</v>
       </c>
@@ -26901,9 +26703,6 @@
       <c r="O134" t="n">
         <v>29</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.5459591726082871</v>
       </c>
@@ -27297,9 +27096,6 @@
       <c r="O136" t="n">
         <v>95</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.9336238180998111</v>
       </c>
@@ -27693,9 +27489,6 @@
       <c r="O138" t="n">
         <v>23</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.433002102413469</v>
       </c>
@@ -28089,9 +27882,6 @@
       <c r="O140" t="n">
         <v>79</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.7763819118935271</v>
       </c>
@@ -28485,9 +28275,6 @@
       <c r="O142" t="n">
         <v>18</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.338871210584454</v>
       </c>
@@ -28881,9 +28668,6 @@
       <c r="O144" t="n">
         <v>57</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.5601742908598867</v>
       </c>
@@ -29277,9 +29061,6 @@
       <c r="O146" t="n">
         <v>11</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.207087962023833</v>
       </c>
@@ -29673,9 +29454,6 @@
       <c r="O148" t="n">
         <v>54</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.5306914334462085</v>
       </c>
@@ -30069,9 +29847,6 @@
       <c r="O150" t="n">
         <v>11</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.207087962023833</v>
       </c>
@@ -30465,9 +30240,6 @@
       <c r="O152" t="n">
         <v>41</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.4029323846536027</v>
       </c>
@@ -30861,9 +30633,6 @@
       <c r="O154" t="n">
         <v>13</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.244740318755439</v>
       </c>
@@ -31257,9 +31026,6 @@
       <c r="O156" t="n">
         <v>29</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.2850009549988897</v>
       </c>
@@ -31653,9 +31419,6 @@
       <c r="O158" t="n">
         <v>8</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.150609426926424</v>
       </c>
@@ -32049,9 +31812,6 @@
       <c r="O160" t="n">
         <v>43</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.4225876229293882</v>
       </c>
@@ -32445,9 +32205,6 @@
       <c r="O162" t="n">
         <v>10</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.18826178365803</v>
       </c>
@@ -32841,9 +32598,6 @@
       <c r="O164" t="n">
         <v>51</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.5012085760325302</v>
       </c>
@@ -33237,9 +32991,6 @@
       <c r="O166" t="n">
         <v>12</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.225914140389636</v>
       </c>
@@ -33633,9 +33384,6 @@
       <c r="O168" t="n">
         <v>60</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.5896571482735649</v>
       </c>
@@ -34029,9 +33777,6 @@
       <c r="O170" t="n">
         <v>28</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.5235865943506316</v>
       </c>
@@ -34425,9 +34170,6 @@
       <c r="O172" t="n">
         <v>100</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.9728454513394866</v>
       </c>
@@ -34821,9 +34563,6 @@
       <c r="O174" t="n">
         <v>26</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.486187551897015</v>
       </c>
@@ -35217,9 +34956,6 @@
       <c r="O176" t="n">
         <v>99</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.9631169968260916</v>
       </c>
@@ -35613,9 +35349,6 @@
       <c r="O178" t="n">
         <v>31</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.5796851580310564</v>
       </c>
@@ -36009,9 +35742,6 @@
       <c r="O180" t="n">
         <v>97</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.943660087799302</v>
       </c>
@@ -36405,9 +36135,6 @@
       <c r="O182" t="n">
         <v>15</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.280492818402124</v>
       </c>
@@ -36801,9 +36528,6 @@
       <c r="O184" t="n">
         <v>89</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.8658324516921432</v>
       </c>
@@ -37197,9 +36921,6 @@
       <c r="O186" t="n">
         <v>17</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.3178918608557406</v>
       </c>
@@ -37593,9 +37314,6 @@
       <c r="O188" t="n">
         <v>75</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.729634088504615</v>
       </c>
@@ -37989,9 +37707,6 @@
       <c r="O190" t="n">
         <v>18</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.3365913820825489</v>
       </c>
@@ -38385,9 +38100,6 @@
       <c r="O192" t="n">
         <v>56</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.5447934527501125</v>
       </c>
@@ -38781,9 +38493,6 @@
       <c r="O194" t="n">
         <v>12</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.2243942547216992</v>
       </c>
@@ -39177,9 +38886,6 @@
       <c r="O196" t="n">
         <v>47</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.4572373621295587</v>
       </c>
@@ -39573,9 +39279,6 @@
       <c r="O198" t="n">
         <v>8</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.1495961698144662</v>
       </c>
@@ -39969,9 +39672,6 @@
       <c r="O200" t="n">
         <v>31</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.3015820899152408</v>
       </c>
@@ -40365,9 +40065,6 @@
       <c r="O202" t="n">
         <v>15</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.280492818402124</v>
       </c>
@@ -40761,9 +40458,6 @@
       <c r="O204" t="n">
         <v>30</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.291853635401846</v>
       </c>
@@ -41157,9 +40851,6 @@
       <c r="O206" t="n">
         <v>18</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.3365913820825489</v>
       </c>
@@ -41553,9 +41244,6 @@
       <c r="O208" t="n">
         <v>42</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.4085950895625844</v>
       </c>
@@ -41949,9 +41637,6 @@
       <c r="O210" t="n">
         <v>16</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.2991923396289323</v>
       </c>
@@ -42345,9 +42030,6 @@
       <c r="O212" t="n">
         <v>39</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.3794097260223998</v>
       </c>
@@ -42741,9 +42423,6 @@
       <c r="O214" t="n">
         <v>22</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.4113894669897819</v>
       </c>
@@ -43136,9 +42815,6 @@
       </c>
       <c r="O216" t="n">
         <v>62</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>0</v>
       </c>
       <c r="R216" t="n">
         <v>0.6031641798304817</v>
